--- a/كشف_درجات_الفصل_الأول_السعودي.xlsx
+++ b/كشف_درجات_الفصل_الأول_السعودي.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jks20\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD47CEC1-5C66-43F2-A8A6-56254C362865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD859F9A-5A70-4671-9569-A878759F2C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -489,86 +489,86 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -971,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.65"/>
   <cols>
     <col min="1" max="1" width="7.796875" style="2" customWidth="1"/>
@@ -983,140 +983,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="H1" s="15"/>
-      <c r="J1" s="15"/>
+      <c r="H1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="H2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="H2" s="31"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="H3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="H3" s="31"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="H4" s="15"/>
-      <c r="J4" s="15"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="H4" s="31"/>
+      <c r="J4" s="31"/>
     </row>
     <row r="5" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="10" t="s">
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="32" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A7" s="17"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="35" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="33" t="s">
+      <c r="G7" s="30"/>
+      <c r="H7" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="34"/>
-      <c r="J7" s="11"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="33"/>
     </row>
     <row r="8" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="17"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="31">
+      <c r="A8" s="11"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="25">
         <v>40</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="29">
+      <c r="G8" s="26"/>
+      <c r="H8" s="23">
         <v>20</v>
       </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="11"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="33"/>
     </row>
     <row r="9" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="23" t="s">
+      <c r="A9" s="11"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="11"/>
+      <c r="J9" s="33"/>
     </row>
     <row r="10" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="12"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="34"/>
     </row>
     <row r="11" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A11" s="6">
@@ -1321,7 +1321,7 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A27" s="8">
+      <c r="A27" s="6">
         <v>17</v>
       </c>
       <c r="B27" s="3"/>
@@ -1373,7 +1373,7 @@
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A31" s="6">
+      <c r="A31" s="8">
         <v>21</v>
       </c>
       <c r="B31" s="3"/>
@@ -1399,7 +1399,7 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A33" s="8">
+      <c r="A33" s="6">
         <v>23</v>
       </c>
       <c r="B33" s="3"/>
@@ -1450,8 +1450,155 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
+    <row r="37" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A37" s="8">
+        <v>27</v>
+      </c>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>28</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A39" s="6">
+        <v>29</v>
+      </c>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>30</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A41" s="6">
+        <v>31</v>
+      </c>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>32</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A43" s="6">
+        <v>33</v>
+      </c>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>34</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A45" s="6">
+        <v>35</v>
+      </c>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>36</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A47" s="8">
+        <v>37</v>
+      </c>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>38</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A49" s="6">
+        <v>39</v>
+      </c>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>40</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A51" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="J6:J10"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="J1:J4"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C3:F3"/>
@@ -1468,10 +1615,6 @@
     <mergeCell ref="E6:E10"/>
     <mergeCell ref="D6:D10"/>
     <mergeCell ref="C6:C10"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="J6:J10"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="J1:J4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
